--- a/artfynd/A 26056-2022 artfynd.xlsx
+++ b/artfynd/A 26056-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26056-2022 artfynd.xlsx
+++ b/artfynd/A 26056-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>60508177</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581571.7658740694</v>
+        <v>581572</v>
       </c>
       <c r="R2" t="n">
-        <v>6442085.034366459</v>
+        <v>6442085</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,19 @@
           <t>Ukna</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-Hf-Väs-0662</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2016-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +789,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
